--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.05312563634727</v>
+        <v>4.071132915906432</v>
       </c>
       <c r="D2" t="n">
-        <v>23.88646253300692</v>
+        <v>3.881550161613625</v>
       </c>
       <c r="E2" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F2" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2.92163119895878</v>
+        <v>0.4747650698308017</v>
       </c>
       <c r="D3" t="n">
-        <v>2.146235473575055</v>
+        <v>0.3487632644559464</v>
       </c>
       <c r="E3" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F3" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.80940467288891</v>
+        <v>4.194028259344448</v>
       </c>
       <c r="D4" t="n">
-        <v>26.98316164394966</v>
+        <v>4.38476376714182</v>
       </c>
       <c r="E4" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F4" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.0181908694219</v>
+        <v>7.477956016281059</v>
       </c>
       <c r="D5" t="n">
-        <v>47.19230343376596</v>
+        <v>7.668749307986969</v>
       </c>
       <c r="E5" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F5" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.52623458342554</v>
+        <v>4.14801311980665</v>
       </c>
       <c r="D6" t="n">
-        <v>25.01175617228027</v>
+        <v>4.064410377995545</v>
       </c>
       <c r="E6" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F6" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.09774869774087</v>
+        <v>5.703384163382891</v>
       </c>
       <c r="D7" t="n">
-        <v>36.2213014196151</v>
+        <v>5.885961480687454</v>
       </c>
       <c r="E7" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F7" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.70346433824903</v>
+        <v>4.989312954965468</v>
       </c>
       <c r="D8" t="n">
-        <v>30.4519991290963</v>
+        <v>4.948449858478149</v>
       </c>
       <c r="E8" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F8" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.97479020260923</v>
+        <v>6.333403407924</v>
       </c>
       <c r="D9" t="n">
-        <v>39.41492922651975</v>
+        <v>6.40492599930946</v>
       </c>
       <c r="E9" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F9" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.54633798787268</v>
+        <v>3.663779923029311</v>
       </c>
       <c r="D10" t="n">
-        <v>22.14756334375609</v>
+        <v>3.598979043360365</v>
       </c>
       <c r="E10" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F10" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>36.58071972973111</v>
+        <v>5.944366956081305</v>
       </c>
       <c r="D11" t="n">
-        <v>36.64310059791916</v>
+        <v>5.954503847161863</v>
       </c>
       <c r="E11" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F11" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>5.804980686100756</v>
+        <v>0.9433093614913729</v>
       </c>
       <c r="D12" t="n">
-        <v>5.799390476730991</v>
+        <v>0.9424009524687861</v>
       </c>
       <c r="E12" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F12" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>29.61037229319618</v>
+        <v>4.811685497644379</v>
       </c>
       <c r="D13" t="n">
-        <v>29.55429456739799</v>
+        <v>4.802572867202174</v>
       </c>
       <c r="E13" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F13" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>28.07530954238008</v>
+        <v>4.562237800636763</v>
       </c>
       <c r="D14" t="n">
-        <v>28.13193316558199</v>
+        <v>4.571439139407073</v>
       </c>
       <c r="E14" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F14" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>29.21302071106914</v>
+        <v>4.747115865548735</v>
       </c>
       <c r="D15" t="n">
-        <v>29.54540018354271</v>
+        <v>4.801127529825691</v>
       </c>
       <c r="E15" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F15" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>22.16798752576102</v>
+        <v>3.602297972936165</v>
       </c>
       <c r="D16" t="n">
-        <v>22.54867080785457</v>
+        <v>3.664159006276368</v>
       </c>
       <c r="E16" t="n">
-        <v>10.85830161207767</v>
+        <v>1.764474011962621</v>
       </c>
       <c r="F16" t="n">
-        <v>11.22567051642583</v>
+        <v>1.824171458919198</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
